--- a/output.xlsx
+++ b/output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,7 +437,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026.02(월)</t>
+          <t>2026.01(원)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2026.03(월)</t>
         </is>
       </c>
     </row>
@@ -457,6 +462,11 @@
           <t>30,321,699</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>31,418,928</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -474,6 +484,11 @@
           <t>23,210,800</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>990,996</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -491,6 +506,11 @@
           <t>103,322,744</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>101,746,634</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -505,6 +525,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>1,682,324</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -522,6 +547,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>2,145,615</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -539,6 +569,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>160,683,182</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -556,6 +591,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>21,175,589</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -573,6 +613,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>21,175,589</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -590,6 +635,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>5,460,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -607,6 +657,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>640,000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -624,6 +679,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>975,840</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -641,6 +701,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>4,952,115</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -658,6 +723,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>800,000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -678,6 +748,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -692,6 +767,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -709,6 +789,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>5,508,805</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -729,6 +814,11 @@
           <t>15,176,753</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>14,550,147</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -746,6 +836,11 @@
           <t>11,442,552</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>9,940,431</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -760,6 +855,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>4,777,533</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -777,6 +877,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>3,925,502</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -794,6 +899,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>311,120</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -811,6 +921,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>62,981</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -831,6 +946,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -848,6 +968,11 @@
           <t>121,934</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>121,793</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -865,6 +990,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -879,6 +1009,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>1,251,335</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -896,6 +1031,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>55,406,557</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -916,6 +1056,11 @@
           <t>29,024,698</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>29,504,530</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -930,6 +1075,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>18,130,693</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -947,6 +1097,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>47,155,391</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -967,6 +1122,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -981,6 +1141,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>237,265,328</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -998,6 +1163,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>284,420,719</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1015,6 +1185,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>237,265,328</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1031,6 +1206,11 @@
         </is>
       </c>
       <c r="C36" t="inlineStr">
+        <is>
+          <t>284,420,719</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1047,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,7 +1238,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026.02(월)</t>
+          <t>2026.01(원)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2026.03(월)</t>
         </is>
       </c>
     </row>
@@ -1078,6 +1263,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1095,6 +1285,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1112,6 +1307,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1129,6 +1329,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1146,6 +1351,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1163,6 +1373,11 @@
           <t>14,648,131</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>15,799,856</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1180,6 +1395,11 @@
           <t>93,477,649</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>92,353,788</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1197,6 +1417,11 @@
           <t>20,875,575</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>21,166,310</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1214,6 +1439,11 @@
           <t>8,767</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,090</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1228,6 +1458,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>17,373,420</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1245,6 +1480,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>12,489,815</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1262,6 +1502,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>48,929</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1279,6 +1524,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>158,922,286</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1299,6 +1549,11 @@
           <t>15,673,568</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>15,619,072</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1316,6 +1571,11 @@
           <t>9,835,231</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>9,214,694</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1330,6 +1590,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>8,041,020</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1347,7 +1612,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>76,810</t>
+          <t>5,760,570</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>5,273,035</t>
         </is>
       </c>
     </row>
@@ -1367,6 +1637,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1381,6 +1656,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>39,310,389</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1401,6 +1681,11 @@
           <t>76,810</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>5,273,035</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1418,6 +1703,11 @@
           <t>9,863</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>178,153</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1432,6 +1722,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>99,336</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1449,6 +1744,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>1,682,324</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1466,6 +1766,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>21,175,589</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1483,6 +1788,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>2,096,686</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1500,6 +1810,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>25,140,608</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1517,6 +1832,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>223,373,283</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1534,7 +1854,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17,373,420</t>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1876,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8,041,020</t>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8,228,610</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1898,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5,760,570</t>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1920,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>99,336</t>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>100,520</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,7 +442,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026.03(월)</t>
+          <t>2026.02(원)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2026.03(원)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2026.04(원)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2026.05(원)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2026.06(월)</t>
         </is>
       </c>
     </row>
@@ -467,6 +487,26 @@
           <t>31,418,928</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>29,943,810</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>31,087,994</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>34,778,854</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>34,778,854</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -489,6 +529,26 @@
           <t>990,996</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>990,636</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>990,636</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5,474,055</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5,474,055</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -511,6 +571,26 @@
           <t>101,746,634</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>102,252,662</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>111,227,894</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>121,766,700</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>121,766,700</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -530,6 +610,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>1,753,109</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1,821,884</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1,913,915</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1,938,933</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -552,6 +652,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2,501,155</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2,649,273</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3,647,831</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3,175,903</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -574,6 +694,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>138,410,822</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>137,658,265</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>148,868,270</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>167,134,445</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -596,6 +736,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>26,181,081</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>27,614,876</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>29,099,235</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>79,505,754</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -618,6 +778,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>26,181,081</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>27,614,876</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>29,099,235</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>79,505,754</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -640,6 +820,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>5,480,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5,500,000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5,520,000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5,540,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -662,6 +862,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>720,000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>800,000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>880,000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>960,000</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -684,6 +904,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>975,840</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>975,840</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>975,840</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -706,6 +946,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>4,952,115</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4,952,115</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4,952,115</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -728,6 +988,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>1,000,000</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1,200,000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1,400,000</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1,600,000</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -753,6 +1033,26 @@
           <t>0</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -775,6 +1075,26 @@
           <t>0</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -797,6 +1117,26 @@
           <t>0</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -819,6 +1159,26 @@
           <t>14,550,147</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>10,726,893</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8,368,601</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8,418,216</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>8,418,216</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -841,6 +1201,26 @@
           <t>9,940,431</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>13,020,088</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>16,037,755</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>12,972,602</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>12,972,602</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -860,6 +1240,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>4,777,533</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4,777,533</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4,777,533</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>4,777,533</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -882,6 +1282,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>3,932,770</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3,936,950</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>3,942,899</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3,948,652</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -904,6 +1324,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>357,938</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>356,137</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1,841,221</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2,969,076</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -926,6 +1366,26 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>10,563</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>860,633</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -951,6 +1411,26 @@
           <t>0</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>200,000</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -973,6 +1453,26 @@
           <t>121,793</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>121,357</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>122,969</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>126,713</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>126,713</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -995,11 +1495,31 @@
           <t>0</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>CMA계좌 자산(성과급 임시 보관)</t>
+          <t>CMA계좌 자산(투자금 임시 보관)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1013,6 +1533,26 @@
         </is>
       </c>
       <c r="D27" t="inlineStr">
+        <is>
+          <t>3,158,415</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1,411,075</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>6,090,230</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1036,6 +1576,26 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>49,977,545</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>48,638,621</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>49,018,933</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>47,403,022</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1061,6 +1621,26 @@
           <t>29,504,530</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>29,928,845</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>33,170,986</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>33,745,465</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>33,745,465</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1080,6 +1660,26 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>18,395,254</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>18,483,114</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>20,504,735</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20,358,680</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1102,6 +1702,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>47,899,784</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>48,411,959</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>53,675,721</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>54,104,145</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1127,6 +1747,26 @@
           <t>0</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1146,6 +1786,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>214,569,448</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>213,911,762</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>226,986,438</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>294,043,221</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1168,6 +1828,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>262,469,232</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>262,323,721</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>280,662,159</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>348,147,366</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1190,6 +1870,26 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>214,569,448</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>213,911,762</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>226,986,438</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>294,043,221</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1211,6 +1911,26 @@
         </is>
       </c>
       <c r="D36" t="inlineStr">
+        <is>
+          <t>262,469,232</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>262,323,721</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>280,662,159</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>348,147,366</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1227,7 +1947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1243,7 +1963,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026.03(월)</t>
+          <t>2026.02(원)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2026.03(원)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2026.04(원)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2026.06(월)</t>
         </is>
       </c>
     </row>
@@ -1268,6 +2003,21 @@
           <t>0</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1287,6 +2037,21 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>110,600</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1312,6 +2077,21 @@
           <t>0</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1331,6 +2111,21 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>1,496,846</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1,260,650</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1,696,060</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1353,6 +2148,21 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>1,607,446</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1,260,650</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1,696,060</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1378,6 +2188,21 @@
           <t>15,799,856</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>15,013,544</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>16,077,315</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>18,979,474</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1400,6 +2225,21 @@
           <t>92,353,788</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>92,859,749</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>102,062,176</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>112,436,022</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1422,6 +2262,21 @@
           <t>21,166,310</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21,585,485</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>24,377,495</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>25,054,470</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1444,6 +2299,21 @@
           <t>9,090</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9,206</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10,681</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10,934</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1466,6 +2336,21 @@
           <t>0</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1485,6 +2370,21 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>12,510,745</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>12,741,170</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>14,784,250</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1507,6 +2407,21 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>527,083</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>22,275</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1,686,062</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1529,6 +2444,21 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>142,366,872</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>142,231,429</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>158,997,979</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1554,6 +2484,21 @@
           <t>15,619,072</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>14,930,266</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>15,010,679</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>15,799,380</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1573,7 +2518,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9,214,694</t>
+          <t>9,214,964</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>9,053,890</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>9,015,058</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>9,089,872</t>
         </is>
       </c>
     </row>
@@ -1595,6 +2555,21 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>8,228,610</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8,231,145</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8,753,355</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1617,7 +2592,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5,273,035</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>27,940</t>
         </is>
       </c>
     </row>
@@ -1642,6 +2632,21 @@
           <t>0</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1661,6 +2666,21 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>33,062,646</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>32,215,301</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>32,779,092</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1683,7 +2703,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5,273,035</t>
+          <t>990,996</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>990,636</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>990,636</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>27,940</t>
         </is>
       </c>
     </row>
@@ -1708,6 +2743,21 @@
           <t>178,153</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>339,023</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>150,660</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>240,806</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1727,6 +2777,21 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>100,520</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>103,009</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>29,455</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1749,6 +2814,21 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>1,642,509</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1,821,884</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1,913,915</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1771,6 +2851,21 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>26,185,275</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>27,614,876</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>29,099,235</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1793,6 +2888,21 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>430,395</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1,366,348</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>265,709</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1815,6 +2925,21 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>29,527,848</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>32,235,776</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>32,449,610</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1837,6 +2962,21 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>206,564,812</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>207,943,156</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>225,922,741</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1859,7 +2999,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,581,440</t>
         </is>
       </c>
     </row>
@@ -1881,7 +3036,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8,228,610</t>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>8,664,630</t>
         </is>
       </c>
     </row>
@@ -1903,7 +3073,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,880,395</t>
         </is>
       </c>
     </row>
@@ -1925,7 +3110,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>100,520</t>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>15,431</t>
         </is>
       </c>
     </row>
